--- a/reports/devops-jobs-israel-2026-W20.xlsx
+++ b/reports/devops-jobs-israel-2026-W20.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="455">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-05-15T14:59:51</t>
+    <t xml:space="preserve">2026-05-15T15:25:18</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -57,12 +57,15 @@
     <t xml:space="preserve">Junior %</t>
   </si>
   <si>
+    <t xml:space="preserve">0.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salary disclosure rate %</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.0%</t>
   </si>
   <si>
-    <t xml:space="preserve">Salary disclosure rate %</t>
-  </si>
-  <si>
     <t xml:space="preserve">Maintained by</t>
   </si>
   <si>
@@ -87,6 +90,9 @@
     <t xml:space="preserve">Jobs</t>
   </si>
   <si>
+    <t xml:space="preserve">linkedin</t>
+  </si>
+  <si>
     <t xml:space="preserve">greenhouse</t>
   </si>
   <si>
@@ -429,6 +435,708 @@
     <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7654285003</t>
   </si>
   <si>
+    <t xml:space="preserve">DevSecOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Terraform, CI/CD, CloudFormation, Security, Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8300354002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fraud Group Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Python, Security, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8413034002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fraud Lead (Technical Architect)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Security, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=8413035002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, GCP, CI/CD, Helm, Grafana, Security, Argo CD, AI/MLOps, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Research Scientist – LTX Model Evaluation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lightricks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.lightricks.com/position?gh_jid=8392230002&amp;gh_jid=8392230002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Product Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4857060101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connecteam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4290904319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DEVOPS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elad Software Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-at-elad-software-systems-4412621606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Penlink</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-penlink-4414226464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nvidia-ai-4412450002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeValue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-codevalue-4413971017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21936 - DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qualitest acq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/21936-devops-engineer-at-qualitest-acq-4414943772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kela Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-kela-technologies-4408746535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deepdub</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-deepdub-4413883243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checkmarx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-checkmarx-4413888362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PayPlus - Payment Gateway</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-payplus-payment-gateway-4413875202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SailPoint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sailpoint-4414928397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coralogix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-coralogix-4403487139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4412719295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eko</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-eko-4414506870</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DataTeam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-datateam-4411159898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autodesk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-autodesk-4403368852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rhino Federated Computing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-rhino-federated-computing-4405650446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevSecOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-engineer-at-wix-4408278376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IVIX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-ivix-4412570472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Horizon Technologies LTD.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-horizon-technologies-ltd-4411164586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer- 239442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-239442-at-experis-4410348697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer (GCP | Kubernetes) – Mid Level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yarden Abramovich HR Consulting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-gcp-kubernetes-%E2%80%93-mid-level-at-yarden-abramovich-hr-consulting-4413282456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-codevalue-4413960785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform Engineer (DevOps)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Redis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-engineer-devops-at-redis-4382514162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Glassbox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-glassbox-4414629081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure and Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silverfort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-and-cloud-engineer-at-silverfort-4399936284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zenity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-zenity-4408672165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Security Engineer (Azure &amp; AI Focus)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KPMG Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-azure-ai-focus-at-kpmg-israel-4413043824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-ai-4412435877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allpha Innovation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-infrastructure-engineer-at-allpha-innovation-4413893764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[S3NS] Site Reliability Engineering - NetDevOps (H/F)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashdod, South District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/s3ns-site-reliability-engineering-netdevops-h-f-at-thales-4410089955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Veeva Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kiryat Ono, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-veeva-systems-4415005984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cato Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-cato-networks-4410623229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Network Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HCLTech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-network-site-reliability-engineer-at-hcltech-4413517183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-matia-4329699733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-system-engineer-at-apple-4414171036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unity South APAC (SEA, ANZ, IND Subcont.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-platform-engineer-at-unity-south-apac-sea-anz-ind-subcont-4413091861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI21 Labs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-ai21-labs-4413404972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Platform (DevOps) Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-devops-engineer-at-wix-4414572643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer- Observability &amp; Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nisha Group - קבוצת נישה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-observability-cloud-at-nisha-group-%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%A0%D7%99%D7%A9%D7%94-4410604039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akeyless Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-infrastructure-engineer-at-akeyless-security-4412366573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Embedded Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/embedded-platform-engineer-at-apple-4414155774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Frontend Infrastructure Engineer (Core Team)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-frontend-infrastructure-engineer-core-team-at-connecteam-4365751301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineer, Cloud Platforms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-cloud-platforms-at-nvidia-4403682415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genpact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-genpact-4410160627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Priority Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-priority-software-4413566885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dialog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-dialog-4410353746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied Materials - Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-applied-materials-israel-4412923466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT OPS / Infrastructure Engineer – Office &amp; Lab Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calanit by one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-ops-infrastructure-engineer-%E2%80%93-office-lab-infrastructure-at-calanit-by-one-4411155298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medulla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-at-medulla-4411492957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-infrastructure-engineer-at-sqlink-group-4411134991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-at-kela-technologies-4410027133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mPrest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-mprest-4399970422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Advanced Technology Leaders, Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Akiva, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-advanced-technology-leaders-inc-4414993344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nexite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-nexite-4414599051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uvision Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emek Hefer Regional Council, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-uvision-group-4414549392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer Senior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NO NAME</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-senior-at-no-name-4410375566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-coralogix-4343793999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-devops-engineer-at-thales-4343562293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Engineer - Tactical Munitions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-engineer-tactical-munitions-at-kela-technologies-4410014250</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior System Expert / Infrastructure Automation Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unilink Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-system-expert-infrastructure-automation-engineer-at-unilink-ltd-4413977166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAI - Israel Aerospace Industries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-iai-israel-aerospace-industries-4411150217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential Careers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-confidential-careers-4412539647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Network Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-infrastructure-engineer-at-comblack-4414601758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nova Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-nova-ltd-4405937004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Security Engineer - Microsoft 365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantum Machines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-security-engineer-microsoft-365-at-quantum-machines-4362195136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intern Cloud Security Engineer - Magshimim</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XM Cyber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/intern-cloud-security-engineer-magshimim-at-xm-cyber-4413104763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freightos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devsecops-at-freightos-4415369163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE Team Leader &amp; Escalation Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cyberint, a Check Point Company</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-team-leader-escalation-manager-at-cyberint-a-check-point-company-4412385653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-ai-4412434844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Head of DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fluent Trade Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-at-fluent-trade-technologies-4372997510</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-unity-south-apac-sea-anz-ind-subcont-4413098703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SolarEdge Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-platform-engineer-at-solaredge-technologies-4413102721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teads</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-teads-4337316899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NetNut.io</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-netnut-io-4403306140</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineering Manager - SRE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tipalti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-manager-sre-at-tipalti-4412578041</t>
+  </si>
+  <si>
     <t xml:space="preserve">Staff Engineer Platform Engineering</t>
   </si>
   <si>
@@ -474,15 +1182,6 @@
     <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-engineering-manager-ai-fleet-management-amp-honk-spotify-1131520</t>
   </si>
   <si>
-    <t xml:space="preserve">Senior Veritas eDiscovery Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contact Government Services, LLC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-senior-veritas-ediscovery-platform-engineer-contact-government-services-llc-1131484</t>
-  </si>
-  <si>
     <t xml:space="preserve">Skill</t>
   </si>
   <si>
@@ -495,18 +1194,12 @@
     <t xml:space="preserve">AWS</t>
   </si>
   <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
     <t xml:space="preserve">GCP</t>
   </si>
   <si>
     <t xml:space="preserve">Azure</t>
   </si>
   <si>
-    <t xml:space="preserve">Observability</t>
-  </si>
-  <si>
     <t xml:space="preserve">Python</t>
   </si>
   <si>
@@ -522,9 +1215,6 @@
     <t xml:space="preserve">Docker</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
     <t xml:space="preserve">Prometheus</t>
   </si>
   <si>
@@ -546,16 +1236,10 @@
     <t xml:space="preserve">Percent</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.3%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">64.7%</t>
+    <t xml:space="preserve">60.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.8%</t>
   </si>
   <si>
     <t xml:space="preserve">Role</t>
@@ -585,30 +1269,18 @@
     <t xml:space="preserve">The Center for Educational Technology (CET)</t>
   </si>
   <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Junior DevOps</t>
   </si>
   <si>
     <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
   </si>
   <si>
-    <t xml:space="preserve">linkedin</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-devops-engineer-at-the-center-for-educational-technology-cet-4401072488</t>
   </si>
   <si>
     <t xml:space="preserve">IT Specialist</t>
   </si>
   <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking</t>
   </si>
   <si>
@@ -630,9 +1302,6 @@
     <t xml:space="preserve">abra</t>
   </si>
   <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Trainee / Bootcamp Grad</t>
   </si>
   <si>
@@ -700,6 +1369,21 @@
   </si>
   <si>
     <t xml:space="preserve">yes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lever</t>
+  </si>
+  <si>
+    <t xml:space="preserve">alljobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">drushim</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jobmaster</t>
+  </si>
+  <si>
+    <t xml:space="preserve">glassdoor</t>
   </si>
 </sst>
 </file>
@@ -824,7 +1508,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>34</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7">
@@ -832,7 +1516,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -840,7 +1524,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>34</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9">
@@ -848,7 +1532,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>42</v>
+        <v>134</v>
       </c>
     </row>
     <row r="10">
@@ -856,7 +1540,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -872,7 +1556,7 @@
         <v>13</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
@@ -881,26 +1565,26 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -909,26 +1593,34 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B19" s="3">
-        <v>30</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B20" s="3">
-        <v>4</v>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" s="3">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -944,15 +1636,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>173</v>
+        <v>403</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>183</v>
+        <v>411</v>
       </c>
       <c r="B2" s="3">
         <v>4</v>
@@ -960,7 +1652,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>210</v>
+        <v>433</v>
       </c>
       <c r="B3" s="3">
         <v>1</v>
@@ -968,7 +1660,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>189</v>
+        <v>416</v>
       </c>
       <c r="B4" s="3">
         <v>1</v>
@@ -976,7 +1668,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>204</v>
+        <v>427</v>
       </c>
       <c r="B5" s="3">
         <v>1</v>
@@ -995,15 +1687,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>154</v>
+        <v>387</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>216</v>
+        <v>439</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>217</v>
+        <v>440</v>
       </c>
       <c r="B2" s="3">
         <v>5</v>
@@ -1011,7 +1703,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>218</v>
+        <v>441</v>
       </c>
       <c r="B3" s="3">
         <v>5</v>
@@ -1019,7 +1711,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>167</v>
+        <v>367</v>
       </c>
       <c r="B4" s="3">
         <v>4</v>
@@ -1027,7 +1719,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>219</v>
+        <v>442</v>
       </c>
       <c r="B5" s="3">
         <v>4</v>
@@ -1035,7 +1727,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>162</v>
+        <v>393</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -1043,7 +1735,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>165</v>
+        <v>396</v>
       </c>
       <c r="B7" s="3">
         <v>3</v>
@@ -1051,7 +1743,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>220</v>
+        <v>443</v>
       </c>
       <c r="B8" s="3">
         <v>3</v>
@@ -1059,7 +1751,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>157</v>
+        <v>390</v>
       </c>
       <c r="B9" s="3">
         <v>3</v>
@@ -1067,7 +1759,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>160</v>
+        <v>392</v>
       </c>
       <c r="B10" s="3">
         <v>3</v>
@@ -1075,7 +1767,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>156</v>
+        <v>389</v>
       </c>
       <c r="B11" s="3">
         <v>3</v>
@@ -1083,7 +1775,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>221</v>
+        <v>444</v>
       </c>
       <c r="B12" s="3">
         <v>3</v>
@@ -1091,7 +1783,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -1099,7 +1791,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>222</v>
+        <v>445</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -1107,7 +1799,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>159</v>
+        <v>391</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -1115,7 +1807,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>166</v>
+        <v>397</v>
       </c>
       <c r="B16" s="3">
         <v>1</v>
@@ -1137,33 +1829,33 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>223</v>
+        <v>446</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>224</v>
+        <v>447</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>225</v>
+        <v>448</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B2" s="3">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C2" s="3">
-        <v>10.4</v>
+        <v>15.2</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>226</v>
+        <v>449</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -1172,15 +1864,105 @@
         <v>23</v>
       </c>
       <c r="B3" s="3">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="C3" s="3">
-        <v>1.5</v>
+        <v>33.5</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>226</v>
+        <v>449</v>
       </c>
       <c r="E3" s="3"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="B4" s="3">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3">
+        <v>3.5</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="E4" s="3"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="3">
+        <v>3</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="E5" s="3"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="B6" s="3">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3">
+        <v>32.1</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="E6" s="3"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="B7" s="3">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3">
+        <v>23.1</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="E7" s="3"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="B8" s="3">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3">
+        <v>15.6</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="E8" s="3"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="B9" s="3">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3">
+        <v>6.3</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="E9" s="3"/>
     </row>
   </sheetData>
 </worksheet>
@@ -1189,9 +1971,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="52" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="37" customWidth="1"/>
+    <col min="1" max="1" width="60" customWidth="1"/>
+    <col min="2" max="2" width="43" customWidth="1"/>
+    <col min="3" max="3" width="54" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -1203,63 +1985,63 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J2" s="3">
         <v>3</v>
@@ -1267,31 +2049,31 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J3" s="3">
         <v>0</v>
@@ -1299,31 +2081,31 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J4" s="3">
         <v>3</v>
@@ -1331,29 +2113,29 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F5" s="3"/>
       <c r="G5" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J5" s="3">
         <v>3</v>
@@ -1361,31 +2143,31 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J6" s="3">
         <v>3</v>
@@ -1393,31 +2175,31 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J7" s="3">
         <v>3</v>
@@ -1425,31 +2207,31 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J8" s="3">
         <v>3</v>
@@ -1457,31 +2239,31 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J9" s="3">
         <v>3</v>
@@ -1489,31 +2271,31 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>64</v>
-      </c>
       <c r="G10" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J10" s="3">
         <v>3</v>
@@ -1521,31 +2303,31 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J11" s="3">
         <v>3</v>
@@ -1553,31 +2335,31 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J12" s="3">
         <v>3</v>
@@ -1585,31 +2367,31 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J13" s="3">
         <v>3</v>
@@ -1617,31 +2399,31 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J14" s="3">
         <v>3</v>
@@ -1649,31 +2431,31 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J15" s="3">
         <v>3</v>
@@ -1681,31 +2463,31 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J16" s="3">
         <v>3</v>
@@ -1713,31 +2495,31 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J17" s="3">
         <v>3</v>
@@ -1745,31 +2527,31 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J18" s="3">
         <v>3</v>
@@ -1777,31 +2559,31 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J19" s="3">
         <v>3</v>
@@ -1809,31 +2591,31 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J20" s="3">
         <v>3</v>
@@ -1841,31 +2623,31 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J21" s="3">
         <v>3</v>
@@ -1873,31 +2655,31 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J22" s="3">
         <v>0</v>
@@ -1905,31 +2687,31 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J23" s="3">
         <v>3</v>
@@ -1937,31 +2719,31 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J24" s="3">
         <v>3</v>
@@ -1969,31 +2751,31 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J25" s="3">
         <v>3</v>
@@ -2001,29 +2783,29 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J26" s="3">
         <v>3</v>
@@ -2031,31 +2813,31 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J27" s="3">
         <v>3</v>
@@ -2063,31 +2845,31 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J28" s="3">
         <v>3</v>
@@ -2095,31 +2877,31 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F29" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>125</v>
-      </c>
       <c r="G29" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J29" s="3">
         <v>3</v>
@@ -2127,31 +2909,31 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J30" s="3">
         <v>3</v>
@@ -2159,31 +2941,31 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J31" s="3">
         <v>3</v>
@@ -2191,95 +2973,95 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>122</v>
+        <v>57</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J32" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D33" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F33" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="E33" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F33" s="3" t="s">
+      <c r="G33" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H33" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="G33" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>146</v>
-      </c>
       <c r="I33" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J33" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F34" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="G34" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H34" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="C34" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>150</v>
-      </c>
       <c r="I34" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J34" s="3">
         <v>3</v>
@@ -2287,36 +3069,2520 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H35" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F35" s="3"/>
-      <c r="G35" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>153</v>
-      </c>
       <c r="I35" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J35" s="3">
         <v>3</v>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J36" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J37" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J38" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J39" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J40" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F43" s="3"/>
+      <c r="G43" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F45" s="3"/>
+      <c r="G45" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F46" s="3"/>
+      <c r="G46" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F47" s="3"/>
+      <c r="G47" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F48" s="3"/>
+      <c r="G48" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F49" s="3"/>
+      <c r="G49" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F50" s="3"/>
+      <c r="G50" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F51" s="3"/>
+      <c r="G51" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="I51" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F52" s="3"/>
+      <c r="G52" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="I53" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F54" s="3"/>
+      <c r="G54" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J54" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="I55" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J55" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F56" s="3"/>
+      <c r="G56" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="I56" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J56" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F57" s="3"/>
+      <c r="G57" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F58" s="3"/>
+      <c r="G58" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F60" s="3"/>
+      <c r="G60" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F61" s="3"/>
+      <c r="G61" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="I61" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F62" s="3"/>
+      <c r="G62" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F63" s="3"/>
+      <c r="G63" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="I63" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F64" s="3"/>
+      <c r="G64" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="I64" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="I65" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F66" s="3"/>
+      <c r="G66" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J66" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F67" s="3"/>
+      <c r="G67" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="I67" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J67" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F68" s="3"/>
+      <c r="G68" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="I68" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F69" s="3"/>
+      <c r="G69" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="I69" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F70" s="3"/>
+      <c r="G70" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="I70" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F71" s="3"/>
+      <c r="G71" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="I71" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F72" s="3"/>
+      <c r="G72" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F73" s="3"/>
+      <c r="G73" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H73" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="I73" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F74" s="3"/>
+      <c r="G74" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="I74" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F75" s="3"/>
+      <c r="G75" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="I75" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F76" s="3"/>
+      <c r="G76" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F77" s="3"/>
+      <c r="G77" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H77" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="I77" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="I78" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J78" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F79" s="3"/>
+      <c r="G79" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H79" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="I79" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J79" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F80" s="3"/>
+      <c r="G80" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H80" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="I80" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J80" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F81" s="3"/>
+      <c r="G81" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F82" s="3"/>
+      <c r="G82" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H82" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="I82" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J82" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F83" s="3"/>
+      <c r="G83" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F84" s="3"/>
+      <c r="G84" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H84" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="I84" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F85" s="3"/>
+      <c r="G85" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H85" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="I85" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F86" s="3"/>
+      <c r="G86" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H86" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="I86" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F87" s="3"/>
+      <c r="G87" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H87" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="I87" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F88" s="3"/>
+      <c r="G88" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H88" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="I88" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F89" s="3"/>
+      <c r="G89" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F90" s="3"/>
+      <c r="G90" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H90" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="I90" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J90" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F91" s="3"/>
+      <c r="G91" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F92" s="3"/>
+      <c r="G92" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H92" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="I92" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F93" s="3"/>
+      <c r="G93" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H93" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="I93" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F94" s="3"/>
+      <c r="G94" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F95" s="3"/>
+      <c r="G95" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H95" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="I95" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J95" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F96" s="3"/>
+      <c r="G96" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F97" s="3"/>
+      <c r="G97" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H97" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="I97" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F98" s="3"/>
+      <c r="G98" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H98" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="I98" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F99" s="3"/>
+      <c r="G99" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H99" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="I99" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F100" s="3"/>
+      <c r="G100" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F101" s="3"/>
+      <c r="G101" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F102" s="3"/>
+      <c r="G102" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J102" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E103" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F103" s="3"/>
+      <c r="G103" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H103" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="I103" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J103" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D104" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E104" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F104" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="G104" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H104" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="I104" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J104" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D105" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E105" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="F105" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="G105" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H105" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="I105" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J105" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="D106" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E106" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F106" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="G106" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H106" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="I106" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J106" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="D107" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E107" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F107" s="3"/>
+      <c r="G107" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H107" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="I107" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J107" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="D108" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E108" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F108" s="3"/>
+      <c r="G108" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H108" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="I108" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J108" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="D109" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="E109" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F109" s="3"/>
+      <c r="G109" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H109" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="I109" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J109" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D110" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E110" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F110" s="3"/>
+      <c r="G110" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H110" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="I110" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J110" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E111" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F111" s="3"/>
+      <c r="G111" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H111" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="I111" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J111" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D112" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="E112" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F112" s="3"/>
+      <c r="G112" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H112" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="I112" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J112" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="D113" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E113" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F113" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="G113" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H113" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="I113" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J113" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="D114" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E114" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F114" s="3"/>
+      <c r="G114" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H114" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="I114" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J114" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="D115" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E115" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F115" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="G115" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H115" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="I115" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J115" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="D116" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="E116" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F116" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="G116" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H116" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="I116" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J116" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="D117" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="E117" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F117" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="G117" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H117" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="I117" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="J117" s="3">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J35"/>
+  <autoFilter ref="A1:J117"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -2352,6 +5618,88 @@
     <hyperlink ref="H33" r:id="rId32"/>
     <hyperlink ref="H34" r:id="rId33"/>
     <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+    <hyperlink ref="H44" r:id="rId43"/>
+    <hyperlink ref="H45" r:id="rId44"/>
+    <hyperlink ref="H46" r:id="rId45"/>
+    <hyperlink ref="H47" r:id="rId46"/>
+    <hyperlink ref="H48" r:id="rId47"/>
+    <hyperlink ref="H49" r:id="rId48"/>
+    <hyperlink ref="H50" r:id="rId49"/>
+    <hyperlink ref="H51" r:id="rId50"/>
+    <hyperlink ref="H52" r:id="rId51"/>
+    <hyperlink ref="H53" r:id="rId52"/>
+    <hyperlink ref="H54" r:id="rId53"/>
+    <hyperlink ref="H55" r:id="rId54"/>
+    <hyperlink ref="H56" r:id="rId55"/>
+    <hyperlink ref="H57" r:id="rId56"/>
+    <hyperlink ref="H58" r:id="rId57"/>
+    <hyperlink ref="H59" r:id="rId58"/>
+    <hyperlink ref="H60" r:id="rId59"/>
+    <hyperlink ref="H61" r:id="rId60"/>
+    <hyperlink ref="H62" r:id="rId61"/>
+    <hyperlink ref="H63" r:id="rId62"/>
+    <hyperlink ref="H64" r:id="rId63"/>
+    <hyperlink ref="H65" r:id="rId64"/>
+    <hyperlink ref="H66" r:id="rId65"/>
+    <hyperlink ref="H67" r:id="rId66"/>
+    <hyperlink ref="H68" r:id="rId67"/>
+    <hyperlink ref="H69" r:id="rId68"/>
+    <hyperlink ref="H70" r:id="rId69"/>
+    <hyperlink ref="H71" r:id="rId70"/>
+    <hyperlink ref="H72" r:id="rId71"/>
+    <hyperlink ref="H73" r:id="rId72"/>
+    <hyperlink ref="H74" r:id="rId73"/>
+    <hyperlink ref="H75" r:id="rId74"/>
+    <hyperlink ref="H76" r:id="rId75"/>
+    <hyperlink ref="H77" r:id="rId76"/>
+    <hyperlink ref="H78" r:id="rId77"/>
+    <hyperlink ref="H79" r:id="rId78"/>
+    <hyperlink ref="H80" r:id="rId79"/>
+    <hyperlink ref="H81" r:id="rId80"/>
+    <hyperlink ref="H82" r:id="rId81"/>
+    <hyperlink ref="H83" r:id="rId82"/>
+    <hyperlink ref="H84" r:id="rId83"/>
+    <hyperlink ref="H85" r:id="rId84"/>
+    <hyperlink ref="H86" r:id="rId85"/>
+    <hyperlink ref="H87" r:id="rId86"/>
+    <hyperlink ref="H88" r:id="rId87"/>
+    <hyperlink ref="H89" r:id="rId88"/>
+    <hyperlink ref="H90" r:id="rId89"/>
+    <hyperlink ref="H91" r:id="rId90"/>
+    <hyperlink ref="H92" r:id="rId91"/>
+    <hyperlink ref="H93" r:id="rId92"/>
+    <hyperlink ref="H94" r:id="rId93"/>
+    <hyperlink ref="H95" r:id="rId94"/>
+    <hyperlink ref="H96" r:id="rId95"/>
+    <hyperlink ref="H97" r:id="rId96"/>
+    <hyperlink ref="H98" r:id="rId97"/>
+    <hyperlink ref="H99" r:id="rId98"/>
+    <hyperlink ref="H100" r:id="rId99"/>
+    <hyperlink ref="H101" r:id="rId100"/>
+    <hyperlink ref="H102" r:id="rId101"/>
+    <hyperlink ref="H103" r:id="rId102"/>
+    <hyperlink ref="H104" r:id="rId103"/>
+    <hyperlink ref="H105" r:id="rId104"/>
+    <hyperlink ref="H106" r:id="rId105"/>
+    <hyperlink ref="H107" r:id="rId106"/>
+    <hyperlink ref="H108" r:id="rId107"/>
+    <hyperlink ref="H109" r:id="rId108"/>
+    <hyperlink ref="H110" r:id="rId109"/>
+    <hyperlink ref="H111" r:id="rId110"/>
+    <hyperlink ref="H112" r:id="rId111"/>
+    <hyperlink ref="H113" r:id="rId112"/>
+    <hyperlink ref="H114" r:id="rId113"/>
+    <hyperlink ref="H115" r:id="rId114"/>
+    <hyperlink ref="H116" r:id="rId115"/>
+    <hyperlink ref="H117" r:id="rId116"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -2359,9 +5707,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="37" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="1" max="1" width="60" customWidth="1"/>
+    <col min="2" max="2" width="43" customWidth="1"/>
+    <col min="3" max="3" width="54" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
@@ -2370,110 +5718,1690 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>142</v>
+        <v>157</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>143</v>
+        <v>57</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>146</v>
+        <v>158</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="D36" s="3"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D37" s="3"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D38" s="3"/>
+      <c r="E38" s="3"/>
+      <c r="F38" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="D39" s="3"/>
+      <c r="E39" s="3"/>
+      <c r="F39" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="D40" s="3"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D41" s="3"/>
+      <c r="E41" s="3"/>
+      <c r="F41" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D42" s="3"/>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D43" s="3"/>
+      <c r="E43" s="3"/>
+      <c r="F43" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D44" s="3"/>
+      <c r="E44" s="3"/>
+      <c r="F44" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D45" s="3"/>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D46" s="3"/>
+      <c r="E46" s="3"/>
+      <c r="F46" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="D47" s="3"/>
+      <c r="E47" s="3"/>
+      <c r="F47" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D48" s="3"/>
+      <c r="E48" s="3"/>
+      <c r="F48" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D49" s="3"/>
+      <c r="E49" s="3"/>
+      <c r="F49" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="D50" s="3"/>
+      <c r="E50" s="3"/>
+      <c r="F50" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D51" s="3"/>
+      <c r="E51" s="3"/>
+      <c r="F51" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="D52" s="3"/>
+      <c r="E52" s="3"/>
+      <c r="F52" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="D53" s="3"/>
+      <c r="E53" s="3"/>
+      <c r="F53" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="D54" s="3"/>
+      <c r="E54" s="3"/>
+      <c r="F54" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="D55" s="3"/>
+      <c r="E55" s="3"/>
+      <c r="F55" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="D56" s="3"/>
+      <c r="E56" s="3"/>
+      <c r="F56" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="D57" s="3"/>
+      <c r="E57" s="3"/>
+      <c r="F57" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D58" s="3"/>
+      <c r="E58" s="3"/>
+      <c r="F58" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="D59" s="3"/>
+      <c r="E59" s="3"/>
+      <c r="F59" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="D60" s="3"/>
+      <c r="E60" s="3"/>
+      <c r="F60" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="D61" s="3"/>
+      <c r="E61" s="3"/>
+      <c r="F61" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="D62" s="3"/>
+      <c r="E62" s="3"/>
+      <c r="F62" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="D63" s="3"/>
+      <c r="E63" s="3"/>
+      <c r="F63" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="D64" s="3"/>
+      <c r="E64" s="3"/>
+      <c r="F64" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="D65" s="3"/>
+      <c r="E65" s="3"/>
+      <c r="F65" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D66" s="3"/>
+      <c r="E66" s="3"/>
+      <c r="F66" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="D67" s="3"/>
+      <c r="E67" s="3"/>
+      <c r="F67" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="D68" s="3"/>
+      <c r="E68" s="3"/>
+      <c r="F68" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="D69" s="3"/>
+      <c r="E69" s="3"/>
+      <c r="F69" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="D70" s="3"/>
+      <c r="E70" s="3"/>
+      <c r="F70" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="D71" s="3"/>
+      <c r="E71" s="3"/>
+      <c r="F71" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D72" s="3"/>
+      <c r="E72" s="3"/>
+      <c r="F72" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D73" s="3"/>
+      <c r="E73" s="3"/>
+      <c r="F73" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="D74" s="3"/>
+      <c r="E74" s="3"/>
+      <c r="F74" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="D75" s="3"/>
+      <c r="E75" s="3"/>
+      <c r="F75" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G75" s="3" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="D76" s="3"/>
+      <c r="E76" s="3"/>
+      <c r="F76" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="D77" s="3"/>
+      <c r="E77" s="3"/>
+      <c r="F77" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D78" s="3"/>
+      <c r="E78" s="3"/>
+      <c r="F78" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D79" s="3"/>
+      <c r="E79" s="3"/>
+      <c r="F79" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G79" s="3" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D80" s="3"/>
+      <c r="E80" s="3"/>
+      <c r="F80" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="D81" s="3"/>
+      <c r="E81" s="3"/>
+      <c r="F81" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="D82" s="3"/>
+      <c r="E82" s="3"/>
+      <c r="F82" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="D83" s="3"/>
+      <c r="E83" s="3"/>
+      <c r="F83" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="D84" s="3"/>
+      <c r="E84" s="3"/>
+      <c r="F84" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>382</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G5"/>
+  <autoFilter ref="A1:G84"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
     <hyperlink ref="G4" r:id="rId3"/>
     <hyperlink ref="G5" r:id="rId4"/>
+    <hyperlink ref="G6" r:id="rId5"/>
+    <hyperlink ref="G7" r:id="rId6"/>
+    <hyperlink ref="G8" r:id="rId7"/>
+    <hyperlink ref="G9" r:id="rId8"/>
+    <hyperlink ref="G10" r:id="rId9"/>
+    <hyperlink ref="G11" r:id="rId10"/>
+    <hyperlink ref="G12" r:id="rId11"/>
+    <hyperlink ref="G13" r:id="rId12"/>
+    <hyperlink ref="G14" r:id="rId13"/>
+    <hyperlink ref="G15" r:id="rId14"/>
+    <hyperlink ref="G16" r:id="rId15"/>
+    <hyperlink ref="G17" r:id="rId16"/>
+    <hyperlink ref="G18" r:id="rId17"/>
+    <hyperlink ref="G19" r:id="rId18"/>
+    <hyperlink ref="G20" r:id="rId19"/>
+    <hyperlink ref="G21" r:id="rId20"/>
+    <hyperlink ref="G22" r:id="rId21"/>
+    <hyperlink ref="G23" r:id="rId22"/>
+    <hyperlink ref="G24" r:id="rId23"/>
+    <hyperlink ref="G25" r:id="rId24"/>
+    <hyperlink ref="G26" r:id="rId25"/>
+    <hyperlink ref="G27" r:id="rId26"/>
+    <hyperlink ref="G28" r:id="rId27"/>
+    <hyperlink ref="G29" r:id="rId28"/>
+    <hyperlink ref="G30" r:id="rId29"/>
+    <hyperlink ref="G31" r:id="rId30"/>
+    <hyperlink ref="G32" r:id="rId31"/>
+    <hyperlink ref="G33" r:id="rId32"/>
+    <hyperlink ref="G34" r:id="rId33"/>
+    <hyperlink ref="G35" r:id="rId34"/>
+    <hyperlink ref="G36" r:id="rId35"/>
+    <hyperlink ref="G37" r:id="rId36"/>
+    <hyperlink ref="G38" r:id="rId37"/>
+    <hyperlink ref="G39" r:id="rId38"/>
+    <hyperlink ref="G40" r:id="rId39"/>
+    <hyperlink ref="G41" r:id="rId40"/>
+    <hyperlink ref="G42" r:id="rId41"/>
+    <hyperlink ref="G43" r:id="rId42"/>
+    <hyperlink ref="G44" r:id="rId43"/>
+    <hyperlink ref="G45" r:id="rId44"/>
+    <hyperlink ref="G46" r:id="rId45"/>
+    <hyperlink ref="G47" r:id="rId46"/>
+    <hyperlink ref="G48" r:id="rId47"/>
+    <hyperlink ref="G49" r:id="rId48"/>
+    <hyperlink ref="G50" r:id="rId49"/>
+    <hyperlink ref="G51" r:id="rId50"/>
+    <hyperlink ref="G52" r:id="rId51"/>
+    <hyperlink ref="G53" r:id="rId52"/>
+    <hyperlink ref="G54" r:id="rId53"/>
+    <hyperlink ref="G55" r:id="rId54"/>
+    <hyperlink ref="G56" r:id="rId55"/>
+    <hyperlink ref="G57" r:id="rId56"/>
+    <hyperlink ref="G58" r:id="rId57"/>
+    <hyperlink ref="G59" r:id="rId58"/>
+    <hyperlink ref="G60" r:id="rId59"/>
+    <hyperlink ref="G61" r:id="rId60"/>
+    <hyperlink ref="G62" r:id="rId61"/>
+    <hyperlink ref="G63" r:id="rId62"/>
+    <hyperlink ref="G64" r:id="rId63"/>
+    <hyperlink ref="G65" r:id="rId64"/>
+    <hyperlink ref="G66" r:id="rId65"/>
+    <hyperlink ref="G67" r:id="rId66"/>
+    <hyperlink ref="G68" r:id="rId67"/>
+    <hyperlink ref="G69" r:id="rId68"/>
+    <hyperlink ref="G70" r:id="rId69"/>
+    <hyperlink ref="G71" r:id="rId70"/>
+    <hyperlink ref="G72" r:id="rId71"/>
+    <hyperlink ref="G73" r:id="rId72"/>
+    <hyperlink ref="G74" r:id="rId73"/>
+    <hyperlink ref="G75" r:id="rId74"/>
+    <hyperlink ref="G76" r:id="rId75"/>
+    <hyperlink ref="G77" r:id="rId76"/>
+    <hyperlink ref="G78" r:id="rId77"/>
+    <hyperlink ref="G79" r:id="rId78"/>
+    <hyperlink ref="G80" r:id="rId79"/>
+    <hyperlink ref="G81" r:id="rId80"/>
+    <hyperlink ref="G82" r:id="rId81"/>
+    <hyperlink ref="G83" r:id="rId82"/>
+    <hyperlink ref="G84" r:id="rId83"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -2487,95 +7415,95 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>154</v>
+        <v>387</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>155</v>
+        <v>388</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>156</v>
+        <v>204</v>
       </c>
       <c r="B2" s="3">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>157</v>
+        <v>389</v>
       </c>
       <c r="B3" s="3">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>100</v>
+        <v>390</v>
       </c>
       <c r="B4" s="3">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>158</v>
+        <v>102</v>
       </c>
       <c r="B5" s="3">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>159</v>
+        <v>391</v>
       </c>
       <c r="B6" s="3">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>160</v>
+        <v>392</v>
       </c>
       <c r="B7" s="3">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>161</v>
+        <v>271</v>
       </c>
       <c r="B8" s="3">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>162</v>
+        <v>393</v>
       </c>
       <c r="B9" s="3">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>163</v>
+        <v>394</v>
       </c>
       <c r="B10" s="3">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>164</v>
+        <v>395</v>
       </c>
       <c r="B11" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>165</v>
+        <v>396</v>
       </c>
       <c r="B12" s="3">
         <v>11</v>
@@ -2583,7 +7511,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>166</v>
+        <v>397</v>
       </c>
       <c r="B13" s="3">
         <v>11</v>
@@ -2591,15 +7519,15 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>167</v>
+        <v>367</v>
       </c>
       <c r="B14" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>168</v>
+        <v>398</v>
       </c>
       <c r="B15" s="3">
         <v>7</v>
@@ -2607,10 +7535,10 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>169</v>
+        <v>399</v>
       </c>
       <c r="B16" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -2620,21 +7548,21 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="34" customWidth="1"/>
+    <col min="1" max="1" width="19" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>170</v>
+        <v>400</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B2" s="3">
         <v>7</v>
@@ -2642,7 +7570,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B3" s="3">
         <v>5</v>
@@ -2650,7 +7578,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B4" s="3">
         <v>4</v>
@@ -2658,39 +7586,39 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="B5" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>53</v>
+        <v>122</v>
       </c>
       <c r="B6" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>63</v>
+        <v>167</v>
       </c>
       <c r="B7" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>104</v>
+        <v>177</v>
       </c>
       <c r="B8" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>130</v>
+        <v>55</v>
       </c>
       <c r="B9" s="3">
         <v>2</v>
@@ -2698,58 +7626,58 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>109</v>
+        <v>65</v>
       </c>
       <c r="B10" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="B11" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="B12" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>137</v>
+        <v>159</v>
       </c>
       <c r="B13" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>142</v>
+        <v>170</v>
       </c>
       <c r="B14" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>148</v>
+        <v>189</v>
       </c>
       <c r="B15" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>152</v>
+        <v>203</v>
       </c>
       <c r="B16" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -2760,23 +7688,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="2" max="2" width="19" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>171</v>
+        <v>401</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>172</v>
+        <v>402</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>170</v>
+        <v>400</v>
       </c>
     </row>
     <row r="2">
@@ -2784,7 +7712,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C2" s="3">
         <v>21.6</v>
@@ -2798,7 +7726,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C3" s="3">
         <v>20.7</v>
@@ -2812,7 +7740,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C4" s="3">
         <v>15.6</v>
@@ -2826,13 +7754,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="C5" s="3">
-        <v>11.3</v>
+        <v>14.0</v>
       </c>
       <c r="D5" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -2840,13 +7768,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="C6" s="3">
-        <v>7.2</v>
+        <v>11.3</v>
       </c>
       <c r="D6" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -2854,10 +7782,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>53</v>
+        <v>106</v>
       </c>
       <c r="C7" s="3">
-        <v>7.0</v>
+        <v>7.2</v>
       </c>
       <c r="D7" s="3">
         <v>2</v>
@@ -2868,10 +7796,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="C8" s="3">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="D8" s="3">
         <v>2</v>
@@ -2882,10 +7810,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="C9" s="3">
-        <v>5.8</v>
+        <v>6.0</v>
       </c>
       <c r="D9" s="3">
         <v>2</v>
@@ -2896,13 +7824,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="C10" s="3">
-        <v>2.9</v>
+        <v>5.8</v>
       </c>
       <c r="D10" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -2910,13 +7838,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>109</v>
+        <v>167</v>
       </c>
       <c r="C11" s="3">
-        <v>2.3</v>
+        <v>4.2</v>
       </c>
       <c r="D11" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -2924,13 +7852,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>137</v>
+        <v>177</v>
       </c>
       <c r="C12" s="3">
-        <v>1.7</v>
+        <v>4.2</v>
       </c>
       <c r="D12" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -2938,13 +7866,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>148</v>
+        <v>203</v>
       </c>
       <c r="C13" s="3">
-        <v>1.6</v>
+        <v>3.1</v>
       </c>
       <c r="D13" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -2952,10 +7880,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>142</v>
+        <v>115</v>
       </c>
       <c r="C14" s="3">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="D14" s="3">
         <v>1</v>
@@ -2966,13 +7894,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>117</v>
+        <v>159</v>
       </c>
       <c r="C15" s="3">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="D15" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -2980,13 +7908,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="C16" s="3">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="D16" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -3003,46 +7931,46 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>173</v>
+        <v>403</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>174</v>
+        <v>404</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>175</v>
+        <v>345</v>
       </c>
       <c r="B2" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>176</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B3" s="3">
-        <v>12</v>
+        <v>70</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>177</v>
+        <v>405</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B4" s="3">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>178</v>
+        <v>406</v>
       </c>
     </row>
   </sheetData>
@@ -3058,49 +7986,81 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>173</v>
+        <v>403</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B2" s="3">
-        <v>23</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>36</v>
+        <v>124</v>
       </c>
       <c r="B3" s="3">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>144</v>
+        <v>38</v>
       </c>
       <c r="B4" s="3">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>122</v>
+        <v>175</v>
       </c>
       <c r="B5" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>110</v>
+        <v>154</v>
       </c>
       <c r="B6" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="B7" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="B8" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B9" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="B10" s="3">
         <v>1</v>
       </c>
     </row>
@@ -3125,34 +8085,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>171</v>
+        <v>401</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>179</v>
+        <v>407</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>180</v>
+        <v>408</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>181</v>
+        <v>409</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2">
@@ -3160,28 +8120,28 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>182</v>
+        <v>410</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>183</v>
+        <v>411</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>184</v>
+        <v>412</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>185</v>
+        <v>413</v>
       </c>
       <c r="J2" s="3"/>
     </row>
@@ -3190,28 +8150,28 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>186</v>
+        <v>414</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>187</v>
+        <v>415</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>188</v>
+        <v>160</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>189</v>
+        <v>416</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>190</v>
+        <v>417</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>191</v>
+        <v>23</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>192</v>
+        <v>418</v>
       </c>
       <c r="J3" s="3"/>
     </row>
@@ -3220,28 +8180,28 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>193</v>
+        <v>419</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>194</v>
+        <v>139</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>195</v>
+        <v>140</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>183</v>
+        <v>411</v>
       </c>
       <c r="F4" s="3">
         <v>47</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>196</v>
+        <v>420</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>197</v>
+        <v>421</v>
       </c>
       <c r="J4" s="3"/>
     </row>
@@ -3250,28 +8210,28 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>198</v>
+        <v>422</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>183</v>
+        <v>411</v>
       </c>
       <c r="F5" s="3">
         <v>44</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>199</v>
+        <v>423</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>200</v>
+        <v>424</v>
       </c>
       <c r="J5" s="3"/>
     </row>
@@ -3280,28 +8240,28 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>201</v>
+        <v>425</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>202</v>
+        <v>426</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>204</v>
+        <v>427</v>
       </c>
       <c r="F6" s="3">
         <v>26</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>205</v>
+        <v>428</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>191</v>
+        <v>23</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>206</v>
+        <v>429</v>
       </c>
       <c r="J6" s="3"/>
     </row>
@@ -3310,28 +8270,28 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>207</v>
+        <v>430</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>208</v>
+        <v>431</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>209</v>
+        <v>432</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>210</v>
+        <v>433</v>
       </c>
       <c r="F7" s="3">
         <v>20</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>211</v>
+        <v>434</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>212</v>
+        <v>435</v>
       </c>
       <c r="J7" s="3"/>
     </row>
@@ -3340,28 +8300,28 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>213</v>
+        <v>436</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>183</v>
+        <v>411</v>
       </c>
       <c r="F8" s="3">
         <v>20</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>214</v>
+        <v>437</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>215</v>
+        <v>438</v>
       </c>
       <c r="J8" s="3"/>
     </row>
